--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,19 +63,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T16:14:48+00:00</t>
+    <t>2026-07-07T17:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Norwegian Institute of Public Health (NIPH)</t>
+    <t>Devotta</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Norwegian Institute of Public Health (NIPH) (https://www.fhi.no/, johan@devotta.no)</t>
+    <t>Devotta (https://www.devotta.no/, johan@devotta.no)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -92,7 +92,7 @@
 one or more ANC Encounters, the pregnancy-level Observations (LMP and EDD,
 once per Bundle) and the visit-level Observations (Gestational Age and
 ANC Visit Number, once per finished Encounter). type = collection (a
-container; the middleware maps it to the DHIS2 tracker model — Patient -&gt;
+container; the middleware maps it to the DHIS2 tracker model: Patient -&gt;
 TrackedEntity, Encounter(finished) -&gt; Event, Encounter(planned) -&gt;
 scheduled Event, Organization -&gt; orgUnit on enrollment + every event).</t>
   </si>
@@ -2677,7 +2677,7 @@
 </t>
   </si>
   <si>
-    <t>Optional. Send ONLY if your data-sharing rules permit — the middleware and SMS gateway do not require a name.</t>
+    <t>Optional. Send ONLY if your data-sharing rules permit; the middleware and SMS gateway do not require a name.</t>
   </si>
   <si>
     <t>A name associated with the individual.</t>
